--- a/EPRC_v3.2_test.xlsx
+++ b/EPRC_v3.2_test.xlsx
@@ -1,154 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connecthkuhk-my.sharepoint.com/personal/u3011514_connect_hku_hk/Documents/Documents/Code/balala/Practice/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_08B58FFC597550CE6B7E4457405986F8B625847E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0506089C-2C6A-C449-9B9B-57D6F6CAF56C}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>IDATE</t>
-  </si>
-  <si>
-    <t>RVD</t>
-  </si>
-  <si>
-    <t>AVGPRICE</t>
-  </si>
-  <si>
-    <t>BORDER_REOPEN</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>B_COMP</t>
-  </si>
-  <si>
-    <t>AGE</t>
-  </si>
-  <si>
-    <t>FLOOR</t>
-  </si>
-  <si>
-    <t>Floor</t>
-  </si>
-  <si>
-    <t>GFL</t>
-  </si>
-  <si>
-    <t>BLOCK_NO</t>
-  </si>
-  <si>
-    <t>DCODE</t>
-  </si>
-  <si>
-    <t>SHOPPING_AREA</t>
-  </si>
-  <si>
-    <t>RESIDENT_AREA</t>
-  </si>
-  <si>
-    <t>GFA</t>
-  </si>
-  <si>
-    <t>STREET</t>
-  </si>
-  <si>
-    <t>ENAME</t>
-  </si>
-  <si>
-    <t>BNAME</t>
-  </si>
-  <si>
-    <t>LATITUDE</t>
-  </si>
-  <si>
-    <t>LONGTITUDE</t>
-  </si>
-  <si>
-    <t>修正纬度</t>
-  </si>
-  <si>
-    <t>修正经度</t>
-  </si>
-  <si>
-    <t>地址来源</t>
-  </si>
-  <si>
-    <t>精确度</t>
-  </si>
-  <si>
-    <t>97/09</t>
-  </si>
-  <si>
-    <t>G/F</t>
-  </si>
-  <si>
-    <t>NT-TM</t>
-  </si>
-  <si>
-    <t>TUEN HI RD 2</t>
-  </si>
-  <si>
-    <t>APPROXIMATE</t>
-  </si>
-  <si>
-    <t>TUEN MUN PARKLANE SQUARE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -163,44 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -488,168 +424,229 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Y2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col min="17" max="17" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.5" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>IDATE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RVD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AVGPRICE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BORDER_REOPEN</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>B_COMP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>AGE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FLOOR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>GFL</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>BLOCK_NO</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>DCODE</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>SHOPPING_AREA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>RESIDENT_AREA</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>GFA</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>STREET</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ENAME</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>BNAME</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>LATITUDE</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>LONGTITUDE</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>修正纬度</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>修正经度</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>地址来源</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>精确度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>42745</v>
+      </c>
+      <c r="C2" t="n">
+        <v>541.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>384780</v>
+      </c>
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F2" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>16/02</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19/F</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HK-CB</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25">
-      <c r="A2">
-        <v>51</v>
-      </c>
-      <c r="B2" s="2">
-        <v>42405</v>
-      </c>
-      <c r="C2">
-        <v>533.9</v>
-      </c>
-      <c r="D2">
-        <v>226707</v>
-      </c>
-      <c r="E2">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>11.48</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>28</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>1752</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2">
-        <v>22.391102386695401</v>
-      </c>
-      <c r="U2">
-        <v>113.97718304513199</v>
-      </c>
-      <c r="V2">
-        <v>22.319303900000001</v>
-      </c>
-      <c r="W2">
-        <v>114.1693611</v>
-      </c>
-      <c r="X2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>29</v>
+      <c r="P2" t="n">
+        <v>1580</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>SHARP ST E 11-13 (SHARP) ST E 11-13</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>SHARP ST E 11-13 (SHARP)</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>22.2779621481711</v>
+      </c>
+      <c r="U2" t="n">
+        <v>114.182387017741</v>
+      </c>
+      <c r="V2" t="n">
+        <v>22.277872</v>
+      </c>
+      <c r="W2" t="n">
+        <v>114.182226</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>BNAME</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>ROOFTOP</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>